--- a/nr-update-card-dp/ig/StructureDefinition-as-organization.xlsx
+++ b/nr-update-card-dp/ig/StructureDefinition-as-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-21T09:29:05+00:00</t>
+    <t>2025-03-21T09:44:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
